--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,17 +117,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,17 +243,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,237 +537,279 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>202435</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21602.33</t>
+          <t>202535</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21613.44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21580.33</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21591.44</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,17 +159,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,17 +285,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,237 +579,279 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>202535</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21613.44</t>
+          <t>202435</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21602.33</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21591.44</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21580.33</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,17 +201,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,17 +327,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,237 +621,279 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>202435</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21602.33</t>
+          <t>202535</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21613.44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21580.33</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21591.44</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,17 +243,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,17 +369,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,237 +663,279 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>202535</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21613.44</t>
+          <t>202635</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21624.56</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21591.44</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21602.56</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,17 +285,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,17 +411,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,237 +705,279 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>202635</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21624.56</t>
+          <t>202735</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21635.67</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>21602.56</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21613.67</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/09 18:49:26</t>
+          <t>06/11 17:56:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,17 +327,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,17 +453,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,237 +747,279 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>202735</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21635.67</t>
+          <t>203735</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21746.78</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>21613.67</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21724.78</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/11 17:56:32</t>
+          <t>06/12 05:48:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/09 18:49:26</t>
+          <t>06/11 17:56:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,17 +369,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,17 +495,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,237 +789,279 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>203735</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21746.78</t>
+          <t>213735</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>22996.78</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21724.78</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>22974.78</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 05:48:26</t>
+          <t>06/12 05:48:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -100,7 +100,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>我也想忘</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/11 17:56:32</t>
+          <t>06/12 05:48:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/09 18:49:26</t>
+          <t>06/11 17:56:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,17 +411,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,17 +537,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,237 +831,279 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>213735</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22996.78</t>
+          <t>223735</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24246.78</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>22974.78</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>24224.78</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -1000,12 +1000,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>06/12 05:49:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1027,83 +1027,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>223735</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24246.78</t>
+          <t>223735</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24246.78</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>24224.78</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>24199.78</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 05:48:52</t>
+          <t>06/12 05:52:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>我也想忘</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/12 05:48:26</t>
+          <t>06/12 05:48:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>我也想忘</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/11 17:56:32</t>
+          <t>06/12 05:48:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/09 18:49:26</t>
+          <t>06/11 17:56:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,17 +453,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,17 +579,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/12 05:49:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>06/12 05:49:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,83 +1069,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>223735</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>24246.78</t>
+          <t>225735</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>24541.33</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>24199.78</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>24494.33</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,17 +75,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 05:52:03</t>
+          <t>06/12 05:52:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>1413.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/12 05:48:52</t>
+          <t>06/12 05:52:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>我也想忘</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/12 05:48:26</t>
+          <t>06/12 05:48:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -184,7 +184,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>我也想忘</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/11 17:56:32</t>
+          <t>06/12 05:48:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/09 18:49:26</t>
+          <t>06/11 17:56:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,17 +495,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,17 +621,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -915,166 +915,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/12 05:49:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>06/12 05:49:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,83 +1111,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>225735</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>24541.33</t>
+          <t>235735</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>25955.17</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>24494.33</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>25908.17</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,27 +75,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 05:52:18</t>
+          <t>06/12 14:43:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1413.84</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/12 05:52:03</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/12 05:48:52</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>我也想忘</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/12 05:48:26</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/11 17:56:32</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/09 18:49:26</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,17 +369,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,17 +411,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,17 +453,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,17 +537,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,17 +579,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,17 +621,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/25 14:57:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/25 14:30:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -828,393 +828,198 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>05/25 15:02:41</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
+          <t>代付</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>费率</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>汇率</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>结算</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>05/25 14:30:42</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>代付</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>05/25 15:05:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>费率</t>
+          <t/>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>汇率</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>05/25 15:02:49</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/12 05:49:26</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
+          <t>202835</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
+          <t>21646.78</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05/25 15:02:49</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>235735</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>25955.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>25908.17</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21624.78</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 14:43:39</t>
+          <t>06/12 15:37:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>4209.89</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/09 18:49:26</t>
+          <t>06/12 14:43:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/09 18:49:22</t>
+          <t>06/09 18:49:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/09 18:46:09</t>
+          <t>06/09 18:49:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/09 18:45:32</t>
+          <t>06/09 18:46:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/09 18:34:39</t>
+          <t>06/09 18:45:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/09 16:28:04</t>
+          <t>06/09 18:34:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,17 +369,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 20:40:28</t>
+          <t>06/09 16:28:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 18:59:08</t>
+          <t>05/26 20:40:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 17:56:05</t>
+          <t>05/26 18:59:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10666.67</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,17 +495,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 11:28:15</t>
+          <t>05/26 17:56:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10666.67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5000/8</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 11:28:03</t>
+          <t>05/26 11:28:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>5000/8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/26 11:12:25</t>
+          <t>05/26 11:28:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>725</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/25 15:02:57</t>
+          <t>05/26 11:12:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/25 15:02:41</t>
+          <t>05/25 15:02:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/25 15:00:41</t>
+          <t>05/25 15:02:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05/25 14:57:54</t>
+          <t>05/25 15:00:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,237 +789,279 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>05/25 14:57:54</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>05/25 14:30:42</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05/25 15:05:21</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>05/25 15:05:21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>05/25 15:02:49</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>202835</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21646.78</t>
+          <t>240724</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25856.67</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21624.78</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>25834.67</t>
         </is>
       </c>
     </row>
